--- a/myAnalyses/0.StateOfHealth/raceAgeExplore2.xlsx
+++ b/myAnalyses/0.StateOfHealth/raceAgeExplore2.xlsx
@@ -14,29 +14,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="23">
   <si>
     <t>sex</t>
   </si>
   <si>
-    <t>ageG</t>
-  </si>
-  <si>
     <t>Asian-NH</t>
   </si>
   <si>
-    <t>Black-NH</t>
-  </si>
-  <si>
     <t>Hisp</t>
   </si>
   <si>
     <t>NHPI-NH</t>
   </si>
   <si>
-    <t>White-NH</t>
-  </si>
-  <si>
     <t>Male</t>
   </si>
   <si>
@@ -73,13 +64,25 @@
     <t>Female</t>
   </si>
   <si>
-    <t>B:W Ratio</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>percent Black to White Black difference</t>
+    <t>Age Group</t>
+  </si>
+  <si>
+    <t>Black</t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>Black:White Rate Ratio</t>
+  </si>
+  <si>
+    <t>percent Black to White difference</t>
+  </si>
+  <si>
+    <t>Black and White All-Cause Age-Specific Death Rates, and Rate Ratios, California 2016-2018</t>
   </si>
 </sst>
 </file>
@@ -89,7 +92,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -221,6 +224,20 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -568,10 +585,25 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -918,667 +950,729 @@
   <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="7" width="9.140625" style="1"/>
-    <col min="9" max="9" width="9.140625" style="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="3" width="0" style="1" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="1"/>
+    <col min="5" max="6" width="0" style="1" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="1"/>
+    <col min="9" max="9" width="13.28515625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="63" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="7"/>
+      <c r="I2" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="7"/>
+      <c r="K2" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1">
+      <c r="C3" s="4">
         <v>77.809756892523595</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="4">
         <v>205.23430257500701</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="4">
         <v>102.06226862217299</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="4">
         <v>125.556338079893</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="4">
         <v>84.249139636812103</v>
       </c>
-      <c r="I3" s="1">
+      <c r="H3" s="2"/>
+      <c r="I3" s="4">
         <f>D3/G3</f>
         <v>2.4360403377381346</v>
       </c>
-      <c r="K3" s="2">
+      <c r="J3" s="2"/>
+      <c r="K3" s="5">
         <f>(D3-G3)/G3</f>
         <v>1.4360403377381346</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="1">
+    <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="4">
         <v>46.404124111707198</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="4">
         <v>150.58018538824999</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="4">
         <v>80.629506323061094</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="4">
         <v>109.058678626462</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="4">
         <v>74.632936222191006</v>
       </c>
-      <c r="I4" s="1">
+      <c r="H4" s="2"/>
+      <c r="I4" s="4">
         <f t="shared" ref="I4:I23" si="0">D4/G4</f>
         <v>2.0176103609263758</v>
       </c>
-      <c r="K4" s="2">
+      <c r="J4" s="2"/>
+      <c r="K4" s="5">
         <f t="shared" ref="K4:K23" si="1">(D4-G4)/G4</f>
         <v>1.0176103609263758</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="1">
+      <c r="C5" s="4">
         <v>66.337949048737997</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="4">
         <v>230.41195140019201</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="4">
         <v>117.57172524932299</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="4">
         <v>137.758894342719</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="4">
         <v>141.485967001445</v>
       </c>
-      <c r="I5" s="1">
+      <c r="H5" s="2"/>
+      <c r="I5" s="4">
         <f t="shared" si="0"/>
         <v>1.6285145183185468</v>
       </c>
-      <c r="K5" s="2">
+      <c r="J5" s="2"/>
+      <c r="K5" s="5">
         <f t="shared" si="1"/>
         <v>0.62851451831854677</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="1">
+    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="4">
         <v>97.572730652230504</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="4">
         <v>340.41991239016102</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="4">
         <v>161.32952484822701</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="4">
         <v>313.622679350152</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="4">
         <v>185.03640304467601</v>
       </c>
-      <c r="I6" s="1">
+      <c r="H6" s="2"/>
+      <c r="I6" s="4">
         <f t="shared" si="0"/>
         <v>1.8397456218815955</v>
       </c>
-      <c r="K6" s="2">
+      <c r="J6" s="2"/>
+      <c r="K6" s="5">
         <f t="shared" si="1"/>
         <v>0.83974562188159552</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="1">
+    <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="4">
         <v>221.39683154812201</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="4">
         <v>664.81678614526504</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="4">
         <v>330.56252671924898</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="4">
         <v>708.86150625745597</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="4">
         <v>414.30330265247397</v>
       </c>
-      <c r="I7" s="1">
+      <c r="H7" s="2"/>
+      <c r="I7" s="4">
         <f t="shared" si="0"/>
         <v>1.604662048042921</v>
       </c>
-      <c r="K7" s="2">
+      <c r="J7" s="2"/>
+      <c r="K7" s="5">
         <f t="shared" si="1"/>
         <v>0.60466204804292101</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="1">
+    <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="4">
         <v>8.2769629686857105</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="4">
         <v>21.317825930526599</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="4">
         <v>11.1631814210755</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="4">
         <v>21.922724014993602</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="4">
         <v>9.8258331572067696</v>
       </c>
-      <c r="I8" s="1">
+      <c r="H8" s="2"/>
+      <c r="I8" s="4">
         <f t="shared" si="0"/>
         <v>2.1695692965121247</v>
       </c>
-      <c r="K8" s="2">
+      <c r="J8" s="2"/>
+      <c r="K8" s="5">
         <f t="shared" si="1"/>
         <v>1.1695692965121245</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="1">
+    <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="4">
         <v>525.16715632700004</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="4">
         <v>1555.63206650081</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="4">
         <v>763.38969419386899</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="4">
         <v>1264.87407344695</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="4">
         <v>937.85050670273199</v>
       </c>
-      <c r="I9" s="1">
+      <c r="H9" s="2"/>
+      <c r="I9" s="4">
         <f t="shared" si="0"/>
         <v>1.6587207186890123</v>
       </c>
-      <c r="K9" s="2">
+      <c r="J9" s="2"/>
+      <c r="K9" s="5">
         <f t="shared" si="1"/>
         <v>0.65872071868901227</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="1">
+    <row r="10" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="4">
         <v>1164.5548077035701</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="4">
         <v>3089.8350569166601</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="4">
         <v>1550.30479633287</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="4">
         <v>2646.2199912433398</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" s="4">
         <v>1870.29776540291</v>
       </c>
-      <c r="I10" s="1">
+      <c r="H10" s="2"/>
+      <c r="I10" s="4">
         <f t="shared" si="0"/>
         <v>1.6520551508283658</v>
       </c>
-      <c r="K10" s="2">
+      <c r="J10" s="2"/>
+      <c r="K10" s="5">
         <f t="shared" si="1"/>
         <v>0.65205515082836574</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="1">
+    <row r="11" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="4">
         <v>3233.97089309887</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="4">
         <v>6047.4119674944805</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="4">
         <v>3915.2392379739199</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="4">
         <v>5878.1553542723304</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" s="4">
         <v>4793.60275093158</v>
       </c>
-      <c r="I11" s="1">
+      <c r="H11" s="2"/>
+      <c r="I11" s="4">
         <f t="shared" si="0"/>
         <v>1.2615588486799907</v>
       </c>
-      <c r="K11" s="2">
+      <c r="J11" s="2"/>
+      <c r="K11" s="5">
         <f t="shared" si="1"/>
         <v>0.26155884867999074</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="1">
+    <row r="12" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="4">
         <v>10158.694062488201</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="4">
         <v>12052.187309319799</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="4">
         <v>10154.668076636501</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="4">
         <v>8819.0461219173994</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" s="4">
         <v>15075.895547845201</v>
       </c>
-      <c r="I12" s="1">
+      <c r="H12" s="2"/>
+      <c r="I12" s="4">
         <f t="shared" si="0"/>
         <v>0.79943425391020428</v>
       </c>
-      <c r="K12" s="2">
+      <c r="J12" s="2"/>
+      <c r="K12" s="5">
         <f t="shared" si="1"/>
         <v>-0.20056574608979569</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K13" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="1">
+    <row r="13" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="4">
         <v>64.245290251134506</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="4">
         <v>175.47297016973101</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="4">
         <v>85.181396839598506</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14" s="4">
         <v>99.454442395059203</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" s="4">
         <v>62.601589276056799</v>
       </c>
-      <c r="I14" s="1">
+      <c r="H14" s="2"/>
+      <c r="I14" s="4">
         <f t="shared" si="0"/>
         <v>2.8030114282872383</v>
       </c>
-      <c r="K14" s="2">
+      <c r="J14" s="2"/>
+      <c r="K14" s="5">
         <f t="shared" si="1"/>
         <v>1.803011428287238</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="1">
+    <row r="15" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="4">
         <v>20.594482097417099</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="4">
         <v>45.5863719850392</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="4">
         <v>26.731828695231801</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15" s="4">
         <v>39.614033323040204</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" s="4">
         <v>29.289172367520599</v>
       </c>
-      <c r="I15" s="1">
+      <c r="H15" s="2"/>
+      <c r="I15" s="4">
         <f t="shared" si="0"/>
         <v>1.5564240400179734</v>
       </c>
-      <c r="K15" s="2">
+      <c r="J15" s="2"/>
+      <c r="K15" s="5">
         <f t="shared" si="1"/>
         <v>0.5564240400179733</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="1">
+    <row r="16" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="4">
         <v>29.333624309625002</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="4">
         <v>100.247666567902</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" s="4">
         <v>44.090695553018797</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16" s="4">
         <v>79.623834306584499</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" s="4">
         <v>60.876663383068703</v>
       </c>
-      <c r="I16" s="1">
+      <c r="H16" s="2"/>
+      <c r="I16" s="4">
         <f t="shared" si="0"/>
         <v>1.6467339206337537</v>
       </c>
-      <c r="K16" s="2">
+      <c r="J16" s="2"/>
+      <c r="K16" s="5">
         <f t="shared" si="1"/>
         <v>0.64673392063375379</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="1">
+    <row r="17" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="4">
         <v>56.190450760857402</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" s="4">
         <v>210.04952423161299</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" s="4">
         <v>79.690091947049396</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17" s="4">
         <v>171.48495135345399</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G17" s="4">
         <v>109.09115521931299</v>
       </c>
-      <c r="I17" s="1">
+      <c r="H17" s="2"/>
+      <c r="I17" s="4">
         <f t="shared" si="0"/>
         <v>1.925449627967885</v>
       </c>
-      <c r="K17" s="2">
+      <c r="J17" s="2"/>
+      <c r="K17" s="5">
         <f t="shared" si="1"/>
         <v>0.92544962796788488</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="1">
+    <row r="18" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="4">
         <v>123.588546710519</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="4">
         <v>464.979026216921</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="4">
         <v>175.652816978624</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F18" s="4">
         <v>491.56740113728802</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G18" s="4">
         <v>267.08696712181899</v>
       </c>
-      <c r="I18" s="1">
+      <c r="H18" s="2"/>
+      <c r="I18" s="4">
         <f t="shared" si="0"/>
         <v>1.740927426102536</v>
       </c>
-      <c r="K18" s="2">
+      <c r="J18" s="2"/>
+      <c r="K18" s="5">
         <f t="shared" si="1"/>
         <v>0.74092742610253604</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="1">
+    <row r="19" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="4">
         <v>9.2484961896221805</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19" s="4">
         <v>14.608132735859201</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E19" s="4">
         <v>8.58596617950157</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F19" s="4">
         <v>7.4838788038760899</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G19" s="4">
         <v>8.5456900197829402</v>
       </c>
-      <c r="I19" s="1">
+      <c r="H19" s="2"/>
+      <c r="I19" s="4">
         <f t="shared" si="0"/>
         <v>1.7094152376276159</v>
       </c>
-      <c r="K19" s="2">
+      <c r="J19" s="2"/>
+      <c r="K19" s="5">
         <f t="shared" si="1"/>
         <v>0.70941523762761594</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" s="1">
+    <row r="20" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="4">
         <v>292.28574122933702</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20" s="4">
         <v>1016.84929923714</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" s="4">
         <v>429.49737579643403</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F20" s="4">
         <v>964.91385895560597</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G20" s="4">
         <v>565.98644952409302</v>
       </c>
-      <c r="I20" s="1">
+      <c r="H20" s="2"/>
+      <c r="I20" s="4">
         <f t="shared" si="0"/>
         <v>1.7965965441260172</v>
       </c>
-      <c r="K20" s="2">
+      <c r="J20" s="2"/>
+      <c r="K20" s="5">
         <f t="shared" si="1"/>
         <v>0.79659654412601733</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" t="s">
+    <row r="21" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="1">
+      <c r="B21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="4">
         <v>673.784515560209</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" s="4">
         <v>1929.1300268902901</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E21" s="4">
         <v>995.36527452230303</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F21" s="4">
         <v>2039.0025982603199</v>
       </c>
-      <c r="G21" s="1">
+      <c r="G21" s="4">
         <v>1240.16867081644</v>
       </c>
-      <c r="I21" s="1">
+      <c r="H21" s="2"/>
+      <c r="I21" s="4">
         <f t="shared" si="0"/>
         <v>1.5555384298010739</v>
       </c>
-      <c r="K21" s="2">
+      <c r="J21" s="2"/>
+      <c r="K21" s="5">
         <f t="shared" si="1"/>
         <v>0.55553842980107393</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" s="1">
+    <row r="22" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="4">
         <v>2208.58827188962</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22" s="4">
         <v>4255.9158453864202</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E22" s="4">
         <v>2788.7574864631702</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F22" s="4">
         <v>4790.3561473022</v>
       </c>
-      <c r="G22" s="1">
+      <c r="G22" s="4">
         <v>3573.0821073028001</v>
       </c>
-      <c r="I22" s="1">
+      <c r="H22" s="2"/>
+      <c r="I22" s="4">
         <f t="shared" si="0"/>
         <v>1.1911049669661995</v>
       </c>
-      <c r="K22" s="2">
+      <c r="J22" s="2"/>
+      <c r="K22" s="5">
         <f t="shared" si="1"/>
         <v>0.1911049669661995</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>18</v>
-      </c>
-      <c r="B23" t="s">
-        <v>17</v>
-      </c>
-      <c r="C23" s="1">
+    <row r="23" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="4">
         <v>8855.1101417205591</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D23" s="4">
         <v>11082.9064577799</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E23" s="4">
         <v>9290.1491928034193</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F23" s="4">
         <v>8461.3261123323791</v>
       </c>
-      <c r="G23" s="1">
+      <c r="G23" s="4">
         <v>13030.010261702801</v>
       </c>
-      <c r="I23" s="1">
+      <c r="H23" s="2"/>
+      <c r="I23" s="4">
         <f t="shared" si="0"/>
         <v>0.85056774593296081</v>
       </c>
-      <c r="K23" s="2">
+      <c r="J23" s="2"/>
+      <c r="K23" s="5">
         <f t="shared" si="1"/>
         <v>-0.14943225406703919</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I3:I12">
-    <cfRule type="dataBar" priority="3">
+    <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -1592,7 +1686,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3:I23">
-    <cfRule type="dataBar" priority="2">
+    <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -1606,7 +1700,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3:K23">
-    <cfRule type="dataBar" priority="1">
+    <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -1619,7 +1713,22 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D3:G23">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{354514F0-5FEA-49EF-B2A8-88690DF54BE9}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -1662,6 +1771,17 @@
           </x14:cfRule>
           <xm:sqref>K3:K23</xm:sqref>
         </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{354514F0-5FEA-49EF-B2A8-88690DF54BE9}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D3:G23</xm:sqref>
+        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>

--- a/myAnalyses/0.StateOfHealth/raceAgeExplore2.xlsx
+++ b/myAnalyses/0.StateOfHealth/raceAgeExplore2.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\0.CBD\myAnalyses\0.StateOfHealth\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="480" yWindow="105" windowWidth="27795" windowHeight="12600"/>
   </bookViews>
   <sheets>
     <sheet name="raceAgetemp" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -88,7 +93,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -656,6 +661,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -703,7 +711,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -738,7 +746,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -956,7 +964,7 @@
     <col min="5" max="6" width="0" style="1" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="9.140625" style="1"/>
     <col min="9" max="9" width="13.28515625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.5703125" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.35">
@@ -1033,32 +1041,32 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C4" s="4">
-        <v>46.404124111707198</v>
+        <v>8.2769629686857105</v>
       </c>
       <c r="D4" s="4">
-        <v>150.58018538824999</v>
+        <v>21.317825930526599</v>
       </c>
       <c r="E4" s="4">
-        <v>80.629506323061094</v>
+        <v>11.1631814210755</v>
       </c>
       <c r="F4" s="4">
-        <v>109.058678626462</v>
+        <v>21.922724014993602</v>
       </c>
       <c r="G4" s="4">
-        <v>74.632936222191006</v>
+        <v>9.8258331572067696</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="4">
-        <f t="shared" ref="I4:I23" si="0">D4/G4</f>
-        <v>2.0176103609263758</v>
+        <f>D4/G4</f>
+        <v>2.1695692965121247</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="5">
-        <f t="shared" ref="K4:K23" si="1">(D4-G4)/G4</f>
-        <v>1.0176103609263758</v>
+        <f>(D4-G4)/G4</f>
+        <v>1.1695692965121245</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -1066,32 +1074,32 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="4">
-        <v>66.337949048737997</v>
+        <v>46.404124111707198</v>
       </c>
       <c r="D5" s="4">
-        <v>230.41195140019201</v>
+        <v>150.58018538824999</v>
       </c>
       <c r="E5" s="4">
-        <v>117.57172524932299</v>
+        <v>80.629506323061094</v>
       </c>
       <c r="F5" s="4">
-        <v>137.758894342719</v>
+        <v>109.058678626462</v>
       </c>
       <c r="G5" s="4">
-        <v>141.485967001445</v>
+        <v>74.632936222191006</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="4">
-        <f t="shared" si="0"/>
-        <v>1.6285145183185468</v>
+        <f t="shared" ref="I5:I23" si="0">D5/G5</f>
+        <v>2.0176103609263758</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="5">
-        <f t="shared" si="1"/>
-        <v>0.62851451831854677</v>
+        <f t="shared" ref="K5:K23" si="1">(D5-G5)/G5</f>
+        <v>1.0176103609263758</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -1099,32 +1107,32 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" s="4">
-        <v>97.572730652230504</v>
+        <v>66.337949048737997</v>
       </c>
       <c r="D6" s="4">
-        <v>340.41991239016102</v>
+        <v>230.41195140019201</v>
       </c>
       <c r="E6" s="4">
-        <v>161.32952484822701</v>
+        <v>117.57172524932299</v>
       </c>
       <c r="F6" s="4">
-        <v>313.622679350152</v>
+        <v>137.758894342719</v>
       </c>
       <c r="G6" s="4">
-        <v>185.03640304467601</v>
+        <v>141.485967001445</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="4">
         <f t="shared" si="0"/>
-        <v>1.8397456218815955</v>
+        <v>1.6285145183185468</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="5">
         <f t="shared" si="1"/>
-        <v>0.83974562188159552</v>
+        <v>0.62851451831854677</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -1132,32 +1140,32 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7" s="4">
-        <v>221.39683154812201</v>
+        <v>97.572730652230504</v>
       </c>
       <c r="D7" s="4">
-        <v>664.81678614526504</v>
+        <v>340.41991239016102</v>
       </c>
       <c r="E7" s="4">
-        <v>330.56252671924898</v>
+        <v>161.32952484822701</v>
       </c>
       <c r="F7" s="4">
-        <v>708.86150625745597</v>
+        <v>313.622679350152</v>
       </c>
       <c r="G7" s="4">
-        <v>414.30330265247397</v>
+        <v>185.03640304467601</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="4">
         <f t="shared" si="0"/>
-        <v>1.604662048042921</v>
+        <v>1.8397456218815955</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="5">
         <f t="shared" si="1"/>
-        <v>0.60466204804292101</v>
+        <v>0.83974562188159552</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -1165,32 +1173,32 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" s="4">
-        <v>8.2769629686857105</v>
+        <v>221.39683154812201</v>
       </c>
       <c r="D8" s="4">
-        <v>21.317825930526599</v>
+        <v>664.81678614526504</v>
       </c>
       <c r="E8" s="4">
-        <v>11.1631814210755</v>
+        <v>330.56252671924898</v>
       </c>
       <c r="F8" s="4">
-        <v>21.922724014993602</v>
+        <v>708.86150625745597</v>
       </c>
       <c r="G8" s="4">
-        <v>9.8258331572067696</v>
+        <v>414.30330265247397</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="4">
         <f t="shared" si="0"/>
-        <v>2.1695692965121247</v>
+        <v>1.604662048042921</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="5">
         <f t="shared" si="1"/>
-        <v>1.1695692965121245</v>
+        <v>0.60466204804292101</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -1378,32 +1386,32 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C15" s="4">
-        <v>20.594482097417099</v>
+        <v>9.2484961896221805</v>
       </c>
       <c r="D15" s="4">
-        <v>45.5863719850392</v>
+        <v>14.608132735859201</v>
       </c>
       <c r="E15" s="4">
-        <v>26.731828695231801</v>
+        <v>8.58596617950157</v>
       </c>
       <c r="F15" s="4">
-        <v>39.614033323040204</v>
+        <v>7.4838788038760899</v>
       </c>
       <c r="G15" s="4">
-        <v>29.289172367520599</v>
+        <v>8.5456900197829402</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="4">
-        <f t="shared" si="0"/>
-        <v>1.5564240400179734</v>
+        <f>D15/G15</f>
+        <v>1.7094152376276159</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="5">
-        <f t="shared" si="1"/>
-        <v>0.5564240400179733</v>
+        <f>(D15-G15)/G15</f>
+        <v>0.70941523762761594</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -1411,32 +1419,32 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C16" s="4">
-        <v>29.333624309625002</v>
+        <v>20.594482097417099</v>
       </c>
       <c r="D16" s="4">
-        <v>100.247666567902</v>
+        <v>45.5863719850392</v>
       </c>
       <c r="E16" s="4">
-        <v>44.090695553018797</v>
+        <v>26.731828695231801</v>
       </c>
       <c r="F16" s="4">
-        <v>79.623834306584499</v>
+        <v>39.614033323040204</v>
       </c>
       <c r="G16" s="4">
-        <v>60.876663383068703</v>
+        <v>29.289172367520599</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="4">
         <f t="shared" si="0"/>
-        <v>1.6467339206337537</v>
+        <v>1.5564240400179734</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="5">
         <f t="shared" si="1"/>
-        <v>0.64673392063375379</v>
+        <v>0.5564240400179733</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -1444,32 +1452,32 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C17" s="4">
-        <v>56.190450760857402</v>
+        <v>29.333624309625002</v>
       </c>
       <c r="D17" s="4">
-        <v>210.04952423161299</v>
+        <v>100.247666567902</v>
       </c>
       <c r="E17" s="4">
-        <v>79.690091947049396</v>
+        <v>44.090695553018797</v>
       </c>
       <c r="F17" s="4">
-        <v>171.48495135345399</v>
+        <v>79.623834306584499</v>
       </c>
       <c r="G17" s="4">
-        <v>109.09115521931299</v>
+        <v>60.876663383068703</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="4">
         <f t="shared" si="0"/>
-        <v>1.925449627967885</v>
+        <v>1.6467339206337537</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="5">
         <f t="shared" si="1"/>
-        <v>0.92544962796788488</v>
+        <v>0.64673392063375379</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -1477,32 +1485,32 @@
         <v>15</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" s="4">
-        <v>123.588546710519</v>
+        <v>56.190450760857402</v>
       </c>
       <c r="D18" s="4">
-        <v>464.979026216921</v>
+        <v>210.04952423161299</v>
       </c>
       <c r="E18" s="4">
-        <v>175.652816978624</v>
+        <v>79.690091947049396</v>
       </c>
       <c r="F18" s="4">
-        <v>491.56740113728802</v>
+        <v>171.48495135345399</v>
       </c>
       <c r="G18" s="4">
-        <v>267.08696712181899</v>
+        <v>109.09115521931299</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="4">
         <f t="shared" si="0"/>
-        <v>1.740927426102536</v>
+        <v>1.925449627967885</v>
       </c>
       <c r="J18" s="2"/>
       <c r="K18" s="5">
         <f t="shared" si="1"/>
-        <v>0.74092742610253604</v>
+        <v>0.92544962796788488</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -1510,32 +1518,32 @@
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C19" s="4">
-        <v>9.2484961896221805</v>
+        <v>123.588546710519</v>
       </c>
       <c r="D19" s="4">
-        <v>14.608132735859201</v>
+        <v>464.979026216921</v>
       </c>
       <c r="E19" s="4">
-        <v>8.58596617950157</v>
+        <v>175.652816978624</v>
       </c>
       <c r="F19" s="4">
-        <v>7.4838788038760899</v>
+        <v>491.56740113728802</v>
       </c>
       <c r="G19" s="4">
-        <v>8.5456900197829402</v>
+        <v>267.08696712181899</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="4">
         <f t="shared" si="0"/>
-        <v>1.7094152376276159</v>
+        <v>1.740927426102536</v>
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="5">
         <f t="shared" si="1"/>
-        <v>0.70941523762761594</v>
+        <v>0.74092742610253604</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
